--- a/Structure_Data/text.9.14/20260914_23/structure_factor_20260914_23.xlsx
+++ b/Structure_Data/text.9.14/20260914_23/structure_factor_20260914_23.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D399"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,4255 @@
         <v>12.6972566286744</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.415714263916016</v>
+      </c>
+      <c r="C30">
+        <v>0.414825439453125</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.415714263916016</v>
+      </c>
+      <c r="C31">
+        <v>0.414825439453125</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.379634857177734</v>
+      </c>
+      <c r="C32">
+        <v>0.375865936279297</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.310768127441406</v>
+      </c>
+      <c r="C33">
+        <v>0.290702819824219</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.278488159179688</v>
+      </c>
+      <c r="C34">
+        <v>0.232784271240234</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.262939453125</v>
+      </c>
+      <c r="C35">
+        <v>0.0351066589355469</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.184581756591797</v>
+      </c>
+      <c r="C36">
+        <v>0.005584716796875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.145126342773438</v>
+      </c>
+      <c r="C37">
+        <v>0.00300979614257812</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.126861572265625</v>
+      </c>
+      <c r="C38">
+        <v>0.00193405151367188</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B39">
+        <v>0.0843391418457031</v>
+      </c>
+      <c r="C39">
+        <v>0.000347137451171875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B40">
+        <v>0.0685806274414062</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B41">
+        <v>0.0589981079101562</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B42">
+        <v>0.0567436218261719</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B43">
+        <v>0.0465545654296875</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44">
+        <v>0.0301322937011719</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B45">
+        <v>0.0316619873046875</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B46">
+        <v>0.0203018188476562</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B47">
+        <v>0.016693115234375</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B48">
+        <v>0.015960693359375</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B49">
+        <v>0.0152397155761719</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B50">
+        <v>0.0089111328125</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B51">
+        <v>0.00555801391601562</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>2.5</v>
+      </c>
+      <c r="B52">
+        <v>0.00328445434570312</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B53">
+        <v>0.00257492065429688</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B54">
+        <v>0.00235748291015625</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>3</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>20670</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>2.63611514271892</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>2.7044891817499</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.05</v>
+      </c>
+      <c r="B71">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.1</v>
+      </c>
+      <c r="B72">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.15</v>
+      </c>
+      <c r="B73">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.2</v>
+      </c>
+      <c r="B74">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.25</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.3</v>
+      </c>
+      <c r="B76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.35</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.4</v>
+      </c>
+      <c r="B78">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.45</v>
+      </c>
+      <c r="B79">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.5</v>
+      </c>
+      <c r="B80">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.55</v>
+      </c>
+      <c r="B81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.6</v>
+      </c>
+      <c r="B82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.65</v>
+      </c>
+      <c r="B83">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.7</v>
+      </c>
+      <c r="B84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.75</v>
+      </c>
+      <c r="B85">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.8</v>
+      </c>
+      <c r="B86">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.9</v>
+      </c>
+      <c r="B88">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.95</v>
+      </c>
+      <c r="B89">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.5</v>
+      </c>
+      <c r="B91">
+        <v>4724</v>
+      </c>
+      <c r="C91">
+        <v>0.228543783260764</v>
+      </c>
+      <c r="D91">
+        <v>0.228543783260764</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>1</v>
+      </c>
+      <c r="B92">
+        <v>3254</v>
+      </c>
+      <c r="C92">
+        <v>0.157426221577165</v>
+      </c>
+      <c r="D92">
+        <v>0.385970004837929</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>1.5</v>
+      </c>
+      <c r="B93">
+        <v>2564</v>
+      </c>
+      <c r="C93">
+        <v>0.124044508950169</v>
+      </c>
+      <c r="D93">
+        <v>0.510014513788099</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>2</v>
+      </c>
+      <c r="B94">
+        <v>1872</v>
+      </c>
+      <c r="C94">
+        <v>0.0905660377358491</v>
+      </c>
+      <c r="D94">
+        <v>0.600580551523948</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>2.5</v>
+      </c>
+      <c r="B95">
+        <v>1506</v>
+      </c>
+      <c r="C95">
+        <v>0.0728592162554427</v>
+      </c>
+      <c r="D95">
+        <v>0.67343976777939</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>3</v>
+      </c>
+      <c r="B96">
+        <v>1221</v>
+      </c>
+      <c r="C96">
+        <v>0.0590711175616836</v>
+      </c>
+      <c r="D96">
+        <v>0.732510885341074</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>3.5</v>
+      </c>
+      <c r="B97">
+        <v>960</v>
+      </c>
+      <c r="C97">
+        <v>0.04644412191582</v>
+      </c>
+      <c r="D97">
+        <v>0.778955007256894</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>4</v>
+      </c>
+      <c r="B98">
+        <v>756</v>
+      </c>
+      <c r="C98">
+        <v>0.0365747460087083</v>
+      </c>
+      <c r="D98">
+        <v>0.815529753265602</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>4.5</v>
+      </c>
+      <c r="B99">
+        <v>640</v>
+      </c>
+      <c r="C99">
+        <v>0.03096274794388</v>
+      </c>
+      <c r="D99">
+        <v>0.846492501209482</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>5</v>
+      </c>
+      <c r="B100">
+        <v>525</v>
+      </c>
+      <c r="C100">
+        <v>0.0253991291727141</v>
+      </c>
+      <c r="D100">
+        <v>0.871891630382196</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>5.5</v>
+      </c>
+      <c r="B101">
+        <v>399</v>
+      </c>
+      <c r="C101">
+        <v>0.0193033381712627</v>
+      </c>
+      <c r="D101">
+        <v>0.891194968553459</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>6</v>
+      </c>
+      <c r="B102">
+        <v>333</v>
+      </c>
+      <c r="C102">
+        <v>0.0161103047895501</v>
+      </c>
+      <c r="D102">
+        <v>0.907305273343009</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>6.5</v>
+      </c>
+      <c r="B103">
+        <v>312</v>
+      </c>
+      <c r="C103">
+        <v>0.0150943396226415</v>
+      </c>
+      <c r="D103">
+        <v>0.922399612965651</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>7</v>
+      </c>
+      <c r="B104">
+        <v>241</v>
+      </c>
+      <c r="C104">
+        <v>0.0116594097726173</v>
+      </c>
+      <c r="D104">
+        <v>0.934059022738268</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>7.5</v>
+      </c>
+      <c r="B105">
+        <v>214</v>
+      </c>
+      <c r="C105">
+        <v>0.0103531688437349</v>
+      </c>
+      <c r="D105">
+        <v>0.944412191582003</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>8</v>
+      </c>
+      <c r="B106">
+        <v>184</v>
+      </c>
+      <c r="C106">
+        <v>0.00890179003386551</v>
+      </c>
+      <c r="D106">
+        <v>0.953313981615868</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>8.5</v>
+      </c>
+      <c r="B107">
+        <v>154</v>
+      </c>
+      <c r="C107">
+        <v>0.00745041122399613</v>
+      </c>
+      <c r="D107">
+        <v>0.960764392839865</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>9</v>
+      </c>
+      <c r="B108">
+        <v>146</v>
+      </c>
+      <c r="C108">
+        <v>0.00706337687469763</v>
+      </c>
+      <c r="D108">
+        <v>0.967827769714562</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>9.5</v>
+      </c>
+      <c r="B109">
+        <v>78</v>
+      </c>
+      <c r="C109">
+        <v>0.00377358490566038</v>
+      </c>
+      <c r="D109">
+        <v>0.971601354620223</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>10</v>
+      </c>
+      <c r="B110">
+        <v>82</v>
+      </c>
+      <c r="C110">
+        <v>0.00396710208030963</v>
+      </c>
+      <c r="D110">
+        <v>0.975568456700532</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>10.5</v>
+      </c>
+      <c r="B111">
+        <v>59</v>
+      </c>
+      <c r="C111">
+        <v>0.00285437832607644</v>
+      </c>
+      <c r="D111">
+        <v>0.978422835026609</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>11</v>
+      </c>
+      <c r="B112">
+        <v>58</v>
+      </c>
+      <c r="C112">
+        <v>0.00280599903241413</v>
+      </c>
+      <c r="D112">
+        <v>0.981228834059023</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>11.5</v>
+      </c>
+      <c r="B113">
+        <v>65</v>
+      </c>
+      <c r="C113">
+        <v>0.00314465408805031</v>
+      </c>
+      <c r="D113">
+        <v>0.984373488147073</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>12</v>
+      </c>
+      <c r="B114">
+        <v>55</v>
+      </c>
+      <c r="C114">
+        <v>0.00266086115142719</v>
+      </c>
+      <c r="D114">
+        <v>0.9870343492985</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>12.5</v>
+      </c>
+      <c r="B115">
+        <v>34</v>
+      </c>
+      <c r="C115">
+        <v>0.00164489598451863</v>
+      </c>
+      <c r="D115">
+        <v>0.988679245283019</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>13</v>
+      </c>
+      <c r="B116">
+        <v>25</v>
+      </c>
+      <c r="C116">
+        <v>0.00120948234155781</v>
+      </c>
+      <c r="D116">
+        <v>0.989888727624577</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>13.5</v>
+      </c>
+      <c r="B117">
+        <v>23</v>
+      </c>
+      <c r="C117">
+        <v>0.00111272375423319</v>
+      </c>
+      <c r="D117">
+        <v>0.99100145137881</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>14</v>
+      </c>
+      <c r="B118">
+        <v>32</v>
+      </c>
+      <c r="C118">
+        <v>0.001548137397194</v>
+      </c>
+      <c r="D118">
+        <v>0.992549588776004</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>14.5</v>
+      </c>
+      <c r="B119">
+        <v>23</v>
+      </c>
+      <c r="C119">
+        <v>0.00111272375423319</v>
+      </c>
+      <c r="D119">
+        <v>0.993662312530237</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>15</v>
+      </c>
+      <c r="B120">
+        <v>26</v>
+      </c>
+      <c r="C120">
+        <v>0.00125786163522013</v>
+      </c>
+      <c r="D120">
+        <v>0.994920174165457</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>15.5</v>
+      </c>
+      <c r="B121">
+        <v>15</v>
+      </c>
+      <c r="C121">
+        <v>0.000725689404934688</v>
+      </c>
+      <c r="D121">
+        <v>0.995645863570392</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>16</v>
+      </c>
+      <c r="B122">
+        <v>12</v>
+      </c>
+      <c r="C122">
+        <v>0.00058055152394775</v>
+      </c>
+      <c r="D122">
+        <v>0.99622641509434</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>16.5</v>
+      </c>
+      <c r="B123">
+        <v>11</v>
+      </c>
+      <c r="C123">
+        <v>0.000532172230285438</v>
+      </c>
+      <c r="D123">
+        <v>0.996758587324625</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>17</v>
+      </c>
+      <c r="B124">
+        <v>11</v>
+      </c>
+      <c r="C124">
+        <v>0.000532172230285438</v>
+      </c>
+      <c r="D124">
+        <v>0.997290759554911</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>17.5</v>
+      </c>
+      <c r="B125">
+        <v>8</v>
+      </c>
+      <c r="C125">
+        <v>0.0003870343492985</v>
+      </c>
+      <c r="D125">
+        <v>0.997677793904209</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>18</v>
+      </c>
+      <c r="B126">
+        <v>14</v>
+      </c>
+      <c r="C126">
+        <v>0.000677310111272375</v>
+      </c>
+      <c r="D126">
+        <v>0.998355104015481</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>18.5</v>
+      </c>
+      <c r="B127">
+        <v>3</v>
+      </c>
+      <c r="C127">
+        <v>0.000145137880986938</v>
+      </c>
+      <c r="D127">
+        <v>0.998500241896468</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>19</v>
+      </c>
+      <c r="B128">
+        <v>5</v>
+      </c>
+      <c r="C128">
+        <v>0.000241896468311563</v>
+      </c>
+      <c r="D128">
+        <v>0.99874213836478</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>19.5</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+      <c r="C129">
+        <v>9.67585873246251e-05</v>
+      </c>
+      <c r="D129">
+        <v>0.998838896952104</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>20</v>
+      </c>
+      <c r="B130">
+        <v>3</v>
+      </c>
+      <c r="C130">
+        <v>0.000145137880986938</v>
+      </c>
+      <c r="D130">
+        <v>0.998984034833091</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>20.5</v>
+      </c>
+      <c r="B131">
+        <v>2</v>
+      </c>
+      <c r="C131">
+        <v>9.67585873246251e-05</v>
+      </c>
+      <c r="D131">
+        <v>0.999080793420416</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>21</v>
+      </c>
+      <c r="B132">
+        <v>5</v>
+      </c>
+      <c r="C132">
+        <v>0.000241896468311563</v>
+      </c>
+      <c r="D132">
+        <v>0.999322689888728</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>21.5</v>
+      </c>
+      <c r="B133">
+        <v>5</v>
+      </c>
+      <c r="C133">
+        <v>0.000241896468311563</v>
+      </c>
+      <c r="D133">
+        <v>0.999564586357039</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>22</v>
+      </c>
+      <c r="B134">
+        <v>5</v>
+      </c>
+      <c r="C134">
+        <v>0.000241896468311563</v>
+      </c>
+      <c r="D134">
+        <v>0.999806482825351</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>24</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135">
+        <v>4.83792936623125e-05</v>
+      </c>
+      <c r="D135">
+        <v>0.999854862119013</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>25.5</v>
+      </c>
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="C136">
+        <v>4.83792936623125e-05</v>
+      </c>
+      <c r="D136">
+        <v>0.999903241412675</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>26</v>
+      </c>
+      <c r="B137">
+        <v>1</v>
+      </c>
+      <c r="C137">
+        <v>4.83792936623125e-05</v>
+      </c>
+      <c r="D137">
+        <v>0.999951620706338</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>26.5</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138">
+        <v>4.83792936623125e-05</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139"/>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>153167</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>0.826519538119374</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>0.434910352902973</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>0.05</v>
+      </c>
+      <c r="B153">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>0.1</v>
+      </c>
+      <c r="B154">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>0.15</v>
+      </c>
+      <c r="B155">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>0.2</v>
+      </c>
+      <c r="B156">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>0.25</v>
+      </c>
+      <c r="B157">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>0.3</v>
+      </c>
+      <c r="B158">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>0.35</v>
+      </c>
+      <c r="B159">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>0.4</v>
+      </c>
+      <c r="B160">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>0.45</v>
+      </c>
+      <c r="B161">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>0.5</v>
+      </c>
+      <c r="B162">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>0.55</v>
+      </c>
+      <c r="B163">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>0.6</v>
+      </c>
+      <c r="B164">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>0.65</v>
+      </c>
+      <c r="B165">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>0.7</v>
+      </c>
+      <c r="B166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>0.75</v>
+      </c>
+      <c r="B167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>0.8</v>
+      </c>
+      <c r="B168">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>0.85</v>
+      </c>
+      <c r="B169">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>0.9</v>
+      </c>
+      <c r="B170">
+        <v>1.4142135623731</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>0.95</v>
+      </c>
+      <c r="B171">
+        <v>1.58113883008419</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>0.5</v>
+      </c>
+      <c r="B173">
+        <v>64158</v>
+      </c>
+      <c r="C173">
+        <v>0.418876128670014</v>
+      </c>
+      <c r="D173">
+        <v>0.418876128670014</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B174">
+        <v>30662</v>
+      </c>
+      <c r="C174">
+        <v>0.200186724294398</v>
+      </c>
+      <c r="D174">
+        <v>0.619062852964411</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B175">
+        <v>12146</v>
+      </c>
+      <c r="C175">
+        <v>0.0792990657256459</v>
+      </c>
+      <c r="D175">
+        <v>0.698361918690057</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>1</v>
+      </c>
+      <c r="B176">
+        <v>9432</v>
+      </c>
+      <c r="C176">
+        <v>0.0615798442223194</v>
+      </c>
+      <c r="D176">
+        <v>0.759941762912377</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B177">
+        <v>14213</v>
+      </c>
+      <c r="C177">
+        <v>0.0927941397298374</v>
+      </c>
+      <c r="D177">
+        <v>0.852735902642214</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B178">
+        <v>5785</v>
+      </c>
+      <c r="C178">
+        <v>0.0377692322758819</v>
+      </c>
+      <c r="D178">
+        <v>0.890505134918096</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B179">
+        <v>4062</v>
+      </c>
+      <c r="C179">
+        <v>0.0265200728616477</v>
+      </c>
+      <c r="D179">
+        <v>0.917025207779744</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>1.5</v>
+      </c>
+      <c r="B180">
+        <v>3748</v>
+      </c>
+      <c r="C180">
+        <v>0.0244700229161634</v>
+      </c>
+      <c r="D180">
+        <v>0.941495230695907</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B181">
+        <v>1586</v>
+      </c>
+      <c r="C181">
+        <v>0.0103547108711407</v>
+      </c>
+      <c r="D181">
+        <v>0.951849941567048</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B182">
+        <v>1106</v>
+      </c>
+      <c r="C182">
+        <v>0.00722087655957223</v>
+      </c>
+      <c r="D182">
+        <v>0.95907081812662</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B183">
+        <v>352</v>
+      </c>
+      <c r="C183">
+        <v>0.00229814516181684</v>
+      </c>
+      <c r="D183">
+        <v>0.961368963288437</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B184">
+        <v>841</v>
+      </c>
+      <c r="C184">
+        <v>0.00549073886672717</v>
+      </c>
+      <c r="D184">
+        <v>0.966859702155164</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B185">
+        <v>914</v>
+      </c>
+      <c r="C185">
+        <v>0.00596734283494486</v>
+      </c>
+      <c r="D185">
+        <v>0.972827044990109</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>2</v>
+      </c>
+      <c r="B186">
+        <v>275</v>
+      </c>
+      <c r="C186">
+        <v>0.00179542590766941</v>
+      </c>
+      <c r="D186">
+        <v>0.974622470897778</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B187">
+        <v>715</v>
+      </c>
+      <c r="C187">
+        <v>0.00466810735994046</v>
+      </c>
+      <c r="D187">
+        <v>0.979290578257719</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B188">
+        <v>376</v>
+      </c>
+      <c r="C188">
+        <v>0.00245483687739526</v>
+      </c>
+      <c r="D188">
+        <v>0.981745415135114</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B189">
+        <v>212</v>
+      </c>
+      <c r="C189">
+        <v>0.00138411015427605</v>
+      </c>
+      <c r="D189">
+        <v>0.98312952528939</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B190">
+        <v>194</v>
+      </c>
+      <c r="C190">
+        <v>0.00126659136759224</v>
+      </c>
+      <c r="D190">
+        <v>0.984396116656982</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B191">
+        <v>300</v>
+      </c>
+      <c r="C191">
+        <v>0.00195864644473026</v>
+      </c>
+      <c r="D191">
+        <v>0.986354763101713</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B192">
+        <v>136</v>
+      </c>
+      <c r="C192">
+        <v>0.000887919721611052</v>
+      </c>
+      <c r="D192">
+        <v>0.987242682823324</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B193">
+        <v>132</v>
+      </c>
+      <c r="C193">
+        <v>0.000861804435681315</v>
+      </c>
+      <c r="D193">
+        <v>0.988104487259005</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>2.5</v>
+      </c>
+      <c r="B194">
+        <v>197</v>
+      </c>
+      <c r="C194">
+        <v>0.00128617783203954</v>
+      </c>
+      <c r="D194">
+        <v>0.989390665091044</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B195">
+        <v>275</v>
+      </c>
+      <c r="C195">
+        <v>0.00179542590766941</v>
+      </c>
+      <c r="D195">
+        <v>0.991186090998714</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B196">
+        <v>96</v>
+      </c>
+      <c r="C196">
+        <v>0.000626766862313684</v>
+      </c>
+      <c r="D196">
+        <v>0.991812857861027</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B197">
+        <v>203</v>
+      </c>
+      <c r="C197">
+        <v>0.00132535076093414</v>
+      </c>
+      <c r="D197">
+        <v>0.993138208621962</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B198">
+        <v>89</v>
+      </c>
+      <c r="C198">
+        <v>0.000581065111936644</v>
+      </c>
+      <c r="D198">
+        <v>0.993719273733898</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B199">
+        <v>26</v>
+      </c>
+      <c r="C199">
+        <v>0.000169749358543289</v>
+      </c>
+      <c r="D199">
+        <v>0.993889023092442</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B200">
+        <v>96</v>
+      </c>
+      <c r="C200">
+        <v>0.000626766862313684</v>
+      </c>
+      <c r="D200">
+        <v>0.994515789954755</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B201">
+        <v>83</v>
+      </c>
+      <c r="C201">
+        <v>0.000541892183042039</v>
+      </c>
+      <c r="D201">
+        <v>0.995057682137797</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B202">
+        <v>68</v>
+      </c>
+      <c r="C202">
+        <v>0.000443959860805526</v>
+      </c>
+      <c r="D202">
+        <v>0.995501641998603</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>3</v>
+      </c>
+      <c r="B203">
+        <v>63</v>
+      </c>
+      <c r="C203">
+        <v>0.000411315753393355</v>
+      </c>
+      <c r="D203">
+        <v>0.995912957751996</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B204">
+        <v>40</v>
+      </c>
+      <c r="C204">
+        <v>0.000261152859297368</v>
+      </c>
+      <c r="D204">
+        <v>0.996174110611294</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B205">
+        <v>86</v>
+      </c>
+      <c r="C205">
+        <v>0.000561478647489342</v>
+      </c>
+      <c r="D205">
+        <v>0.996735589258783</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B206">
+        <v>32</v>
+      </c>
+      <c r="C206">
+        <v>0.000208922287437895</v>
+      </c>
+      <c r="D206">
+        <v>0.996944511546221</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B207">
+        <v>90</v>
+      </c>
+      <c r="C207">
+        <v>0.000587593933419079</v>
+      </c>
+      <c r="D207">
+        <v>0.99753210547964</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B208">
+        <v>39</v>
+      </c>
+      <c r="C208">
+        <v>0.000254624037814934</v>
+      </c>
+      <c r="D208">
+        <v>0.997786729517455</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B209">
+        <v>21</v>
+      </c>
+      <c r="C209">
+        <v>0.000137105251131118</v>
+      </c>
+      <c r="D209">
+        <v>0.997923834768586</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B210">
+        <v>19</v>
+      </c>
+      <c r="C210">
+        <v>0.00012404760816625</v>
+      </c>
+      <c r="D210">
+        <v>0.998047882376752</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B211">
+        <v>51</v>
+      </c>
+      <c r="C211">
+        <v>0.000332969895604145</v>
+      </c>
+      <c r="D211">
+        <v>0.998380852272356</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B212">
+        <v>25</v>
+      </c>
+      <c r="C212">
+        <v>0.000163220537060855</v>
+      </c>
+      <c r="D212">
+        <v>0.998544072809417</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>3.46410161513775</v>
+      </c>
+      <c r="B213">
+        <v>5</v>
+      </c>
+      <c r="C213">
+        <v>3.2644107412171e-05</v>
+      </c>
+      <c r="D213">
+        <v>0.998576716916829</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>3.5</v>
+      </c>
+      <c r="B214">
+        <v>38</v>
+      </c>
+      <c r="C214">
+        <v>0.0002480952163325</v>
+      </c>
+      <c r="D214">
+        <v>0.998824812133162</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B215">
+        <v>42</v>
+      </c>
+      <c r="C215">
+        <v>0.000274210502262237</v>
+      </c>
+      <c r="D215">
+        <v>0.999099022635424</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>3.57071421427143</v>
+      </c>
+      <c r="B216">
+        <v>24</v>
+      </c>
+      <c r="C216">
+        <v>0.000156691715578421</v>
+      </c>
+      <c r="D216">
+        <v>0.999255714351002</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>3.60555127546399</v>
+      </c>
+      <c r="B217">
+        <v>9</v>
+      </c>
+      <c r="C217">
+        <v>5.87593933419079e-05</v>
+      </c>
+      <c r="D217">
+        <v>0.999314473744344</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>3.64005494464026</v>
+      </c>
+      <c r="B218">
+        <v>26</v>
+      </c>
+      <c r="C218">
+        <v>0.000169749358543289</v>
+      </c>
+      <c r="D218">
+        <v>0.999484223102888</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>3.67423461417477</v>
+      </c>
+      <c r="B219">
+        <v>26</v>
+      </c>
+      <c r="C219">
+        <v>0.000169749358543289</v>
+      </c>
+      <c r="D219">
+        <v>0.999653972461431</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>3.74165738677394</v>
+      </c>
+      <c r="B220">
+        <v>8</v>
+      </c>
+      <c r="C220">
+        <v>5.22305718594736e-05</v>
+      </c>
+      <c r="D220">
+        <v>0.99970620303329</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>3.77491721763537</v>
+      </c>
+      <c r="B221">
+        <v>4</v>
+      </c>
+      <c r="C221">
+        <v>2.61152859297368e-05</v>
+      </c>
+      <c r="D221">
+        <v>0.99973231831922</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>3.80788655293195</v>
+      </c>
+      <c r="B222">
+        <v>7</v>
+      </c>
+      <c r="C222">
+        <v>4.57017503770394e-05</v>
+      </c>
+      <c r="D222">
+        <v>0.999778020069597</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>3.8405728739343</v>
+      </c>
+      <c r="B223">
+        <v>10</v>
+      </c>
+      <c r="C223">
+        <v>6.52882148243421e-05</v>
+      </c>
+      <c r="D223">
+        <v>0.999843308284422</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>3.90512483795333</v>
+      </c>
+      <c r="B224">
+        <v>8</v>
+      </c>
+      <c r="C224">
+        <v>5.22305718594736e-05</v>
+      </c>
+      <c r="D224">
+        <v>0.999895538856281</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>3.93700393700591</v>
+      </c>
+      <c r="B225">
+        <v>5</v>
+      </c>
+      <c r="C225">
+        <v>3.2644107412171e-05</v>
+      </c>
+      <c r="D225">
+        <v>0.999928182963693</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>4</v>
+      </c>
+      <c r="B226">
+        <v>3</v>
+      </c>
+      <c r="C226">
+        <v>1.95864644473026e-05</v>
+      </c>
+      <c r="D226">
+        <v>0.999947769428141</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>4.03112887414927</v>
+      </c>
+      <c r="B227">
+        <v>4</v>
+      </c>
+      <c r="C227">
+        <v>2.61152859297368e-05</v>
+      </c>
+      <c r="D227">
+        <v>0.99997388471407</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>4.06201920231798</v>
+      </c>
+      <c r="B228">
+        <v>3</v>
+      </c>
+      <c r="C228">
+        <v>1.95864644473026e-05</v>
+      </c>
+      <c r="D228">
+        <v>0.999993471178518</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>4.12310562561766</v>
+      </c>
+      <c r="B229">
+        <v>1</v>
+      </c>
+      <c r="C229">
+        <v>6.52882148243421e-06</v>
+      </c>
+      <c r="D229">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230"/>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B235">
+        <v>0.415714263916016</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B236">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>0</v>
+      </c>
+      <c r="B241">
+        <v>0.415714263916016</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+      <c r="D241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>0.5</v>
+      </c>
+      <c r="B242">
+        <v>0.337375640869141</v>
+      </c>
+      <c r="C242">
+        <v>6</v>
+      </c>
+      <c r="D242">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>1</v>
+      </c>
+      <c r="B243">
+        <v>0.300070249117338</v>
+      </c>
+      <c r="C243">
+        <v>26</v>
+      </c>
+      <c r="D243">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>1.5</v>
+      </c>
+      <c r="B244">
+        <v>0.255599636501736</v>
+      </c>
+      <c r="C244">
+        <v>90</v>
+      </c>
+      <c r="D244">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>2</v>
+      </c>
+      <c r="B245">
+        <v>0.226062205300402</v>
+      </c>
+      <c r="C245">
+        <v>134</v>
+      </c>
+      <c r="D245">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>2.5</v>
+      </c>
+      <c r="B246">
+        <v>0.205676352330881</v>
+      </c>
+      <c r="C246">
+        <v>258</v>
+      </c>
+      <c r="D246">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>3</v>
+      </c>
+      <c r="B247">
+        <v>0.194215393066406</v>
+      </c>
+      <c r="C247">
+        <v>410</v>
+      </c>
+      <c r="D247">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>3.5</v>
+      </c>
+      <c r="B248">
+        <v>0.189733173200476</v>
+      </c>
+      <c r="C248">
+        <v>494</v>
+      </c>
+      <c r="D248">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>4</v>
+      </c>
+      <c r="B249">
+        <v>0.188683473891106</v>
+      </c>
+      <c r="C249">
+        <v>690</v>
+      </c>
+      <c r="D249">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>4.5</v>
+      </c>
+      <c r="B250">
+        <v>0.188557765587947</v>
+      </c>
+      <c r="C250">
+        <v>962</v>
+      </c>
+      <c r="D250">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>5</v>
+      </c>
+      <c r="B251">
+        <v>0.187686204476</v>
+      </c>
+      <c r="C251">
+        <v>1098</v>
+      </c>
+      <c r="D251">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>5.5</v>
+      </c>
+      <c r="B252">
+        <v>0.186187792977432</v>
+      </c>
+      <c r="C252">
+        <v>1406</v>
+      </c>
+      <c r="D252">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>6</v>
+      </c>
+      <c r="B253">
+        <v>0.184536144609536</v>
+      </c>
+      <c r="C253">
+        <v>1578</v>
+      </c>
+      <c r="D253">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>6.5</v>
+      </c>
+      <c r="B254">
+        <v>0.183056958957517</v>
+      </c>
+      <c r="C254">
+        <v>2018</v>
+      </c>
+      <c r="D254">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>7</v>
+      </c>
+      <c r="B255">
+        <v>0.181659063246391</v>
+      </c>
+      <c r="C255">
+        <v>2342</v>
+      </c>
+      <c r="D255">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>7.5</v>
+      </c>
+      <c r="B256">
+        <v>0.180474283483414</v>
+      </c>
+      <c r="C256">
+        <v>2634</v>
+      </c>
+      <c r="D256">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>8</v>
+      </c>
+      <c r="B257">
+        <v>0.179381821668189</v>
+      </c>
+      <c r="C257">
+        <v>2930</v>
+      </c>
+      <c r="D257">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>8.5</v>
+      </c>
+      <c r="B258">
+        <v>0.178438898677478</v>
+      </c>
+      <c r="C258">
+        <v>3402</v>
+      </c>
+      <c r="D258">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>9</v>
+      </c>
+      <c r="B259">
+        <v>0.177609644310242</v>
+      </c>
+      <c r="C259">
+        <v>3926</v>
+      </c>
+      <c r="D259">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>9.5</v>
+      </c>
+      <c r="B260">
+        <v>0.176824187874738</v>
+      </c>
+      <c r="C260">
+        <v>4266</v>
+      </c>
+      <c r="D260">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>10</v>
+      </c>
+      <c r="B261">
+        <v>0.176170545904631</v>
+      </c>
+      <c r="C261">
+        <v>4730</v>
+      </c>
+      <c r="D261">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>10.5</v>
+      </c>
+      <c r="B262">
+        <v>0.175468425439187</v>
+      </c>
+      <c r="C262">
+        <v>5510</v>
+      </c>
+      <c r="D262">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>11</v>
+      </c>
+      <c r="B263">
+        <v>0.17483999505398</v>
+      </c>
+      <c r="C263">
+        <v>5562</v>
+      </c>
+      <c r="D263">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>11.5</v>
+      </c>
+      <c r="B264">
+        <v>0.174265688034748</v>
+      </c>
+      <c r="C264">
+        <v>6410</v>
+      </c>
+      <c r="D264">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>12</v>
+      </c>
+      <c r="B265">
+        <v>0.173722562908884</v>
+      </c>
+      <c r="C265">
+        <v>6894</v>
+      </c>
+      <c r="D265">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>12.5</v>
+      </c>
+      <c r="B266">
+        <v>0.173226654704645</v>
+      </c>
+      <c r="C266">
+        <v>7490</v>
+      </c>
+      <c r="D266">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>13</v>
+      </c>
+      <c r="B267">
+        <v>0.172836232572238</v>
+      </c>
+      <c r="C267">
+        <v>8258</v>
+      </c>
+      <c r="D267">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>13.5</v>
+      </c>
+      <c r="B268">
+        <v>0.172457943764267</v>
+      </c>
+      <c r="C268">
+        <v>8994</v>
+      </c>
+      <c r="D268">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>14</v>
+      </c>
+      <c r="B269">
+        <v>0.172109893436985</v>
+      </c>
+      <c r="C269">
+        <v>9446</v>
+      </c>
+      <c r="D269">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>14.5</v>
+      </c>
+      <c r="B270">
+        <v>0.171789870087239</v>
+      </c>
+      <c r="C270">
+        <v>9978</v>
+      </c>
+      <c r="D270">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>15</v>
+      </c>
+      <c r="B271">
+        <v>0.171456809445458</v>
+      </c>
+      <c r="C271">
+        <v>11138</v>
+      </c>
+      <c r="D271">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>15.5</v>
+      </c>
+      <c r="B272">
+        <v>0.171206547715215</v>
+      </c>
+      <c r="C272">
+        <v>11406</v>
+      </c>
+      <c r="D272">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>16</v>
+      </c>
+      <c r="B273">
+        <v>0.170968817223611</v>
+      </c>
+      <c r="C273">
+        <v>12575</v>
+      </c>
+      <c r="D273">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>16.5</v>
+      </c>
+      <c r="B274">
+        <v>0.170857448506623</v>
+      </c>
+      <c r="C274">
+        <v>12848</v>
+      </c>
+      <c r="D274">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>17</v>
+      </c>
+      <c r="B275">
+        <v>0.170773573538557</v>
+      </c>
+      <c r="C275">
+        <v>12060</v>
+      </c>
+      <c r="D275">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>17.5</v>
+      </c>
+      <c r="B276">
+        <v>0.17073890404231</v>
+      </c>
+      <c r="C276">
+        <v>11804</v>
+      </c>
+      <c r="D276">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>18</v>
+      </c>
+      <c r="B277">
+        <v>0.170762583580931</v>
+      </c>
+      <c r="C277">
+        <v>11016</v>
+      </c>
+      <c r="D277">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>18.5</v>
+      </c>
+      <c r="B278">
+        <v>0.17080072064266</v>
+      </c>
+      <c r="C278">
+        <v>10700</v>
+      </c>
+      <c r="D278">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>19</v>
+      </c>
+      <c r="B279">
+        <v>0.170822801234146</v>
+      </c>
+      <c r="C279">
+        <v>9756</v>
+      </c>
+      <c r="D279">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>19.5</v>
+      </c>
+      <c r="B280">
+        <v>0.170822950828003</v>
+      </c>
+      <c r="C280">
+        <v>9224</v>
+      </c>
+      <c r="D280">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>20</v>
+      </c>
+      <c r="B281">
+        <v>0.170812975214732</v>
+      </c>
+      <c r="C281">
+        <v>8408</v>
+      </c>
+      <c r="D281">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>20.5</v>
+      </c>
+      <c r="B282">
+        <v>0.170780353883998</v>
+      </c>
+      <c r="C282">
+        <v>7452</v>
+      </c>
+      <c r="D282">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>21</v>
+      </c>
+      <c r="B283">
+        <v>0.170763111114502</v>
+      </c>
+      <c r="C283">
+        <v>7040</v>
+      </c>
+      <c r="D283">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>21.5</v>
+      </c>
+      <c r="B284">
+        <v>0.17082412300241</v>
+      </c>
+      <c r="C284">
+        <v>5820</v>
+      </c>
+      <c r="D284">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>22</v>
+      </c>
+      <c r="B285">
+        <v>0.171053372054804</v>
+      </c>
+      <c r="C285">
+        <v>4880</v>
+      </c>
+      <c r="D285">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>22.5</v>
+      </c>
+      <c r="B286">
+        <v>0.171187391126059</v>
+      </c>
+      <c r="C286">
+        <v>3936</v>
+      </c>
+      <c r="D286">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>23</v>
+      </c>
+      <c r="B287">
+        <v>0.171301726938765</v>
+      </c>
+      <c r="C287">
+        <v>2999</v>
+      </c>
+      <c r="D287">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>23.5</v>
+      </c>
+      <c r="B288">
+        <v>0.171303407861552</v>
+      </c>
+      <c r="C288">
+        <v>2180</v>
+      </c>
+      <c r="D288">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>24</v>
+      </c>
+      <c r="B289">
+        <v>0.171437477771147</v>
+      </c>
+      <c r="C289">
+        <v>1620</v>
+      </c>
+      <c r="D289">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>24.5</v>
+      </c>
+      <c r="B290">
+        <v>0.171657315942625</v>
+      </c>
+      <c r="C290">
+        <v>1208</v>
+      </c>
+      <c r="D290">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>25</v>
+      </c>
+      <c r="B291">
+        <v>0.17160682921197</v>
+      </c>
+      <c r="C291">
+        <v>942</v>
+      </c>
+      <c r="D291">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>25.5</v>
+      </c>
+      <c r="B292">
+        <v>0.171643936470763</v>
+      </c>
+      <c r="C292">
+        <v>584</v>
+      </c>
+      <c r="D292">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>26</v>
+      </c>
+      <c r="B293">
+        <v>0.171658932323187</v>
+      </c>
+      <c r="C293">
+        <v>284</v>
+      </c>
+      <c r="D293">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>26.5</v>
+      </c>
+      <c r="B294">
+        <v>0.171726743380229</v>
+      </c>
+      <c r="C294">
+        <v>192</v>
+      </c>
+      <c r="D294">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>27</v>
+      </c>
+      <c r="B295">
+        <v>0.171886737530048</v>
+      </c>
+      <c r="C295">
+        <v>104</v>
+      </c>
+      <c r="D295">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>27.5</v>
+      </c>
+      <c r="B296">
+        <v>0.172264734903971</v>
+      </c>
+      <c r="C296">
+        <v>24</v>
+      </c>
+      <c r="D296">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>28</v>
+      </c>
+      <c r="B297">
+        <v>0.172538757324219</v>
+      </c>
+      <c r="C297">
+        <v>1</v>
+      </c>
+      <c r="D297">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>0</v>
+      </c>
+      <c r="B299">
+        <v>0.415714263916016</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>0.5</v>
+      </c>
+      <c r="B300">
+        <v>0.336864471435547</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>1</v>
+      </c>
+      <c r="B301">
+        <v>0.281810760498047</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>1.5</v>
+      </c>
+      <c r="B302">
+        <v>0.241199493408203</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>2</v>
+      </c>
+      <c r="B303">
+        <v>0.217144012451172</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>2.5</v>
+      </c>
+      <c r="B304">
+        <v>0.200084686279297</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>3</v>
+      </c>
+      <c r="B305">
+        <v>0.196300506591797</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>3.5</v>
+      </c>
+      <c r="B306">
+        <v>0.193641662597656</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>4</v>
+      </c>
+      <c r="B307">
+        <v>0.196434020996094</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>4.5</v>
+      </c>
+      <c r="B308">
+        <v>0.196506500244141</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>5</v>
+      </c>
+      <c r="B309">
+        <v>0.194866180419922</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>5.5</v>
+      </c>
+      <c r="B310">
+        <v>0.19219970703125</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>6</v>
+      </c>
+      <c r="B311">
+        <v>0.189002990722656</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>6.5</v>
+      </c>
+      <c r="B312">
+        <v>0.186515808105469</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>7</v>
+      </c>
+      <c r="B313">
+        <v>0.184532165527344</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>7.5</v>
+      </c>
+      <c r="B314">
+        <v>0.183113098144531</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>8</v>
+      </c>
+      <c r="B315">
+        <v>0.182498931884766</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>8.5</v>
+      </c>
+      <c r="B316">
+        <v>0.182361602783203</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>9</v>
+      </c>
+      <c r="B317">
+        <v>0.182674407958984</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>9.5</v>
+      </c>
+      <c r="B318">
+        <v>0.183490753173828</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>10</v>
+      </c>
+      <c r="B319">
+        <v>0.184585571289062</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>10.5</v>
+      </c>
+      <c r="B320">
+        <v>0.185291290283203</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>11</v>
+      </c>
+      <c r="B321">
+        <v>0.184703826904297</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>11.5</v>
+      </c>
+      <c r="B322">
+        <v>0.183025360107422</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>12</v>
+      </c>
+      <c r="B323">
+        <v>0.181484222412109</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>12.5</v>
+      </c>
+      <c r="B324">
+        <v>0.179885864257812</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>13</v>
+      </c>
+      <c r="B325">
+        <v>0.17828369140625</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>13.5</v>
+      </c>
+      <c r="B326">
+        <v>0.176849365234375</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>14</v>
+      </c>
+      <c r="B327">
+        <v>0.176082611083984</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>14.5</v>
+      </c>
+      <c r="B328">
+        <v>0.175926208496094</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>15</v>
+      </c>
+      <c r="B329">
+        <v>0.175334930419922</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>15.5</v>
+      </c>
+      <c r="B330">
+        <v>0.174839019775391</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>16</v>
+      </c>
+      <c r="B331">
+        <v>0.174324035644531</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>0</v>
+      </c>
+      <c r="B333">
+        <v>0.415714263916016</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>0.5</v>
+      </c>
+      <c r="B334">
+        <v>0.335700988769531</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>1</v>
+      </c>
+      <c r="B335">
+        <v>0.280498504638672</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>1.5</v>
+      </c>
+      <c r="B336">
+        <v>0.239173889160156</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>2</v>
+      </c>
+      <c r="B337">
+        <v>0.21417236328125</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>2.5</v>
+      </c>
+      <c r="B338">
+        <v>0.196197509765625</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>3</v>
+      </c>
+      <c r="B339">
+        <v>0.19012451171875</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>3.5</v>
+      </c>
+      <c r="B340">
+        <v>0.184368133544922</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>4</v>
+      </c>
+      <c r="B341">
+        <v>0.183719635009766</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>4.5</v>
+      </c>
+      <c r="B342">
+        <v>0.181789398193359</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>5</v>
+      </c>
+      <c r="B343">
+        <v>0.180469512939453</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>5.5</v>
+      </c>
+      <c r="B344">
+        <v>0.179817199707031</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>6</v>
+      </c>
+      <c r="B345">
+        <v>0.179622650146484</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>6.5</v>
+      </c>
+      <c r="B346">
+        <v>0.179538726806641</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>7</v>
+      </c>
+      <c r="B347">
+        <v>0.178359985351562</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>7.5</v>
+      </c>
+      <c r="B348">
+        <v>0.177013397216797</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>8</v>
+      </c>
+      <c r="B349">
+        <v>0.176448822021484</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>8.5</v>
+      </c>
+      <c r="B350">
+        <v>0.175685882568359</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>9</v>
+      </c>
+      <c r="B351">
+        <v>0.175151824951172</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>9.5</v>
+      </c>
+      <c r="B352">
+        <v>0.174549102783203</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>10</v>
+      </c>
+      <c r="B353">
+        <v>0.173423767089844</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>10.5</v>
+      </c>
+      <c r="B354">
+        <v>0.172523498535156</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>11</v>
+      </c>
+      <c r="B355">
+        <v>0.172206878662109</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>11.5</v>
+      </c>
+      <c r="B356">
+        <v>0.172138214111328</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>12</v>
+      </c>
+      <c r="B357">
+        <v>0.172172546386719</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>12.5</v>
+      </c>
+      <c r="B358">
+        <v>0.17230224609375</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>13</v>
+      </c>
+      <c r="B359">
+        <v>0.172183990478516</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>13.5</v>
+      </c>
+      <c r="B360">
+        <v>0.171833038330078</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>14</v>
+      </c>
+      <c r="B361">
+        <v>0.171939849853516</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>14.5</v>
+      </c>
+      <c r="B362">
+        <v>0.171947479248047</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>15</v>
+      </c>
+      <c r="B363">
+        <v>0.171836853027344</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>15.5</v>
+      </c>
+      <c r="B364">
+        <v>0.171772003173828</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>16</v>
+      </c>
+      <c r="B365">
+        <v>0.171638488769531</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>0</v>
+      </c>
+      <c r="B367">
+        <v>0.415714263916016</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>0.5</v>
+      </c>
+      <c r="B368">
+        <v>0.339561462402344</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>1</v>
+      </c>
+      <c r="B369">
+        <v>0.285076141357422</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>1.5</v>
+      </c>
+      <c r="B370">
+        <v>0.2431640625</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>2</v>
+      </c>
+      <c r="B371">
+        <v>0.216728210449219</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>2.5</v>
+      </c>
+      <c r="B372">
+        <v>0.197113037109375</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>3</v>
+      </c>
+      <c r="B373">
+        <v>0.191062927246094</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>3.5</v>
+      </c>
+      <c r="B374">
+        <v>0.1864013671875</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <v>4</v>
+      </c>
+      <c r="B375">
+        <v>0.187824249267578</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <v>4.5</v>
+      </c>
+      <c r="B376">
+        <v>0.187488555908203</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <v>5</v>
+      </c>
+      <c r="B377">
+        <v>0.186527252197266</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>5.5</v>
+      </c>
+      <c r="B378">
+        <v>0.184623718261719</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>6</v>
+      </c>
+      <c r="B379">
+        <v>0.182777404785156</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>6.5</v>
+      </c>
+      <c r="B380">
+        <v>0.180862426757812</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>7</v>
+      </c>
+      <c r="B381">
+        <v>0.179718017578125</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382">
+        <v>7.5</v>
+      </c>
+      <c r="B382">
+        <v>0.178070068359375</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383">
+        <v>8</v>
+      </c>
+      <c r="B383">
+        <v>0.176101684570312</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384">
+        <v>8.5</v>
+      </c>
+      <c r="B384">
+        <v>0.173873901367188</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385">
+        <v>9</v>
+      </c>
+      <c r="B385">
+        <v>0.171970367431641</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386">
+        <v>9.5</v>
+      </c>
+      <c r="B386">
+        <v>0.170257568359375</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387">
+        <v>10</v>
+      </c>
+      <c r="B387">
+        <v>0.168895721435547</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388">
+        <v>10.5</v>
+      </c>
+      <c r="B388">
+        <v>0.167633056640625</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389">
+        <v>11</v>
+      </c>
+      <c r="B389">
+        <v>0.166820526123047</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390">
+        <v>11.5</v>
+      </c>
+      <c r="B390">
+        <v>0.165931701660156</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391">
+        <v>12</v>
+      </c>
+      <c r="B391">
+        <v>0.166305541992188</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392">
+        <v>12.5</v>
+      </c>
+      <c r="B392">
+        <v>0.166828155517578</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393">
+        <v>13</v>
+      </c>
+      <c r="B393">
+        <v>0.167182922363281</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394">
+        <v>13.5</v>
+      </c>
+      <c r="B394">
+        <v>0.166831970214844</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395">
+        <v>14</v>
+      </c>
+      <c r="B395">
+        <v>0.167232513427734</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396">
+        <v>14.5</v>
+      </c>
+      <c r="B396">
+        <v>0.166816711425781</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397">
+        <v>15</v>
+      </c>
+      <c r="B397">
+        <v>0.166545867919922</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398">
+        <v>15.5</v>
+      </c>
+      <c r="B398">
+        <v>0.166271209716797</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399">
+        <v>16</v>
+      </c>
+      <c r="B399">
+        <v>0.166557312011719</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>